--- a/backend/outputs/protocol_restore_test_220444_220444.xlsx
+++ b/backend/outputs/protocol_restore_test_220444_220444.xlsx
@@ -1,48 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuanyuqing/Documents/code/schoolProject/backend/outputs/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB372A62-A71C-1E43-AACC-3130F448BD36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="23260" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="协议模板（公开）.docx" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="协议模板（公开）.docx" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>信源系统码</t>
+  </si>
+  <si>
+    <t>信源机器码</t>
+  </si>
+  <si>
+    <t>信宿系统码</t>
+  </si>
+  <si>
+    <t>信宿机器码</t>
+  </si>
+  <si>
+    <t>子地址或消息地址</t>
+  </si>
+  <si>
+    <t>数据段长度（总线为字，其他为字节）</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>内容</t>
+  </si>
+  <si>
+    <t>子内容</t>
+  </si>
+  <si>
+    <t>类型（bit）</t>
+  </si>
+  <si>
+    <t>转换类型</t>
+  </si>
+  <si>
+    <t>判读公式（暂不设计）</t>
+  </si>
+  <si>
+    <t>转换公式（变量必须为x）</t>
+  </si>
+  <si>
+    <t>单位</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>BC</t>
+  </si>
+  <si>
+    <t>RT3</t>
+  </si>
+  <si>
+    <t>飞行计时时间</t>
+  </si>
+  <si>
+    <t>UINT32</t>
+  </si>
+  <si>
+    <t>0~0xFFFFFFFF</t>
+  </si>
+  <si>
+    <t>接收XX指令后，完成时标清零</t>
+  </si>
+  <si>
+    <t>控制指令1</t>
+  </si>
+  <si>
+    <t>UINT16</t>
+  </si>
+  <si>
+    <t>0x1701：供电
+0x1702：断电
+其他值无效</t>
+  </si>
+  <si>
+    <t>接收组播地址</t>
+  </si>
+  <si>
+    <t>消息ID</t>
+  </si>
+  <si>
+    <t>控制指令2</t>
+  </si>
+  <si>
+    <t>控制指令3</t>
+  </si>
+  <si>
+    <t>CRC校验字</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>序号1~4所有字节的CRC值，计算公式见附录C</t>
+  </si>
+  <si>
+    <t>该时间为软件运行计时时间</t>
+  </si>
+  <si>
+    <t>PD状态</t>
+  </si>
+  <si>
+    <t>UINT8</t>
+  </si>
+  <si>
+    <t>0xAA：接通状态；
+0x55：未接通状态；其他值无效。</t>
+  </si>
+  <si>
+    <t>PD控制指令</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PD器状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -82,86 +211,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -451,308 +521,204 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col width="12.33203125" bestFit="1" customWidth="1" min="2" max="5"/>
-    <col width="19.21875" bestFit="1" customWidth="1" min="6" max="6"/>
-    <col width="40.109375" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="23.88671875" bestFit="1" customWidth="1" min="13" max="13"/>
-    <col width="27.44140625" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col min="2" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>名称</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>信源系统码</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>信源机器码</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>信宿系统码</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>信宿机器码</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>子地址或消息地址</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>数据段长度（总线为字，其他为字节）</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>子内容</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>类型（bit）</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>转换类型</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>判读公式（暂不设计）</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>转换公式（变量必须为x）</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>单位</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
+    <row r="1" spans="1:16">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>控制指令</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>BC</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>RT3</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2">
         <v>7</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>3</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>飞行计时时间</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2">
         <v>32</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>UINT32</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0~0xFFFFFFFF</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>接收XX指令后，完成时标清零</t>
-        </is>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="3">
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>控制指令1</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
+    <row r="3" spans="1:16">
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3">
         <v>16</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>UINT16</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0x1701：供电
-0x1702：断电
-其他值无效</t>
-        </is>
+      <c r="L3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="4">
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>接收组播地址</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>消息ID</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>控制指令2</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
+    <row r="4" spans="1:16">
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4">
         <v>16</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>UINT16</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0x1701：供电
-0x1702：断电
-其他值无效</t>
-        </is>
+      <c r="L4" t="s">
+        <v>23</v>
+      </c>
+      <c r="O4" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="5">
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>控制指令3</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
+    <row r="5" spans="1:16">
+      <c r="I5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5">
         <v>16</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>UINT16</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0x1701：供电
-0x1702：断电
-其他值无效</t>
-        </is>
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+      <c r="O5" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="6">
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>CRC校验字</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
+    <row r="6" spans="1:16">
+      <c r="I6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6">
         <v>16</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>UINT16</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>序号1~4所有字节的CRC值，计算公式见附录C</t>
-        </is>
+      <c r="L6" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" t="s">
+        <v>30</v>
+      </c>
+      <c r="P6" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>器状态</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>飞行计时时间</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
+    <row r="7" spans="1:16">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7">
         <v>32</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>UINT32</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>0~0xFFFFFFFF</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>该时间为软件运行计时时间</t>
-        </is>
+      <c r="L7" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7" t="s">
+        <v>20</v>
+      </c>
+      <c r="P7" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="8">
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>PD状态</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
+    <row r="8" spans="1:16">
+      <c r="I8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8">
         <v>8</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>UINT8</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0xAA：接通状态；
-0x55：未接通状态；其他值无效。</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="L8" t="s">
+        <v>34</v>
+      </c>
+      <c r="O8" t="s">
+        <v>35</v>
+      </c>
+      <c r="P8" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="1200" verticalDpi="1200"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
 </worksheet>
 </file>